--- a/aop-2026-27/CFI_AOP_Budget_2026-27_v4.xlsx
+++ b/aop-2026-27/CFI_AOP_Budget_2026-27_v4.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">New city deployments &amp; police integration</t>
   </si>
   <si>
-    <t xml:space="preserve">ANPR feeds, digital billboards, campaign-rule setup &amp; go-live support for Gurugram, Pune, Ahmedabad (the 'upcoming' cities in the SATARK briefing)</t>
+    <t xml:space="preserve">Software-side go-lives for the 30-city scale target (Gurugram, Pune, Ahmedabad first). ASSUMES camera/billboard/infra costs are borne by city police &amp; partners - CFI funds integration, rules setup &amp; go-live support (~Rs 0.7L/city; validate)</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud, ULIP API &amp; data infrastructure</t>
@@ -267,7 +267,7 @@
     <t xml:space="preserve">District process mapping &amp; comparative notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Stage-wise pipeline audit (Gurugram deep-dive) + SW Delhi/Jaipur comparative documentation</t>
+    <t xml:space="preserve">Stage-wise pipeline audit (Gurugram deep-dive) + comparative mapping toward 8+ districts by Jun 2027 (SW Delhi, Jaipur, watchlist)</t>
   </si>
   <si>
     <t xml:space="preserve">Victim narratives, scheme audit report &amp; public brief</t>
@@ -426,7 +426,7 @@
     <t xml:space="preserve">Civic &amp; GovTech</t>
   </si>
   <si>
-    <t xml:space="preserve">NEW vertical, set at exactly Rs 1.00 Cr per Akhtar's instruction. Covers SATARK (live: Jaipur + Bengaluru; upcoming per briefing: Gurugram, Pune, Ahmedabad) + the four open data products. SATARK docs contain NO cost data - every line here is a planning assumption to be validated against actual engineering &amp; deployment quotes.</t>
+    <t xml:space="preserve">NEW vertical, set at exactly Rs 1.00 Cr per Akhtar's instruction. Target: SATARK scaled to 30 cities by Jun 2027 (live today: Jaipur + Bengaluru) + four open data products + exploration of new govtech/DPG opportunities. SATARK docs contain NO cost data - every line is a planning assumption. CRITICAL: Rs 1 Cr funds the software/integration side only; a 30-city rollout assumes city-side infra (ANPR cameras, billboards) is funded by police/partners. Validate before board sign-off.</t>
   </si>
   <si>
     <t xml:space="preserve">Hit &amp; Run</t>
@@ -1913,7 +1913,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
         <v>11</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
         <v>133</v>
       </c>
